--- a/Hoadon/HD2026/HDVao/7/3502551856_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/7/3502551856_HDDienTuDaCapMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/07/2026 đến ngày 27/07/2026</t>
+          <t>Từ ngày 01/07/2026 đến ngày 28/07/2026</t>
         </is>
       </c>
     </row>

--- a/Hoadon/HD2026/HDVao/7/3502551856_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/7/3502551856_HDDienTuDaCapMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/07/2026 đến ngày 28/07/2026</t>
+          <t>Từ ngày 01/07/2026 đến ngày 31/07/2026</t>
         </is>
       </c>
     </row>
@@ -574,27 +574,27 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C26TKN</t>
+          <t>C26TAA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>1102099705</t>
+          <t>1102090036</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
+          <t>CÔNG TY TNHH THẢO KHÁNH TÂM</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -609,11 +609,11 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>9.56E7</v>
+        <v>6.75E7</v>
       </c>
       <c r="L10" s="13" t="n">
         <v>0.0</v>
@@ -623,7 +623,7 @@
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>9.56E7</v>
+        <v>6.75E7</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,27 +657,27 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C26TSV</t>
+          <t>C26TKN</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3500898348</t>
+          <t>1102099705</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -696,17 +696,17 @@
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>2500000.0</v>
+        <v>9.56E7</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>200000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>2700000.0</v>
+        <v>9.56E7</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,27 +740,27 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C26TYY</t>
+          <t>C26TSV</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3604022523</t>
+          <t>3500898348</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HƯNG THỊNH RICE</t>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -775,38 +775,121 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1.276E7</v>
+        <v>2500000.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0.0</v>
+        <v>200000.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
+        <v>2700000.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C26TYY</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3604022523</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HƯNG THỊNH RICE</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
         <v>1.276E7</v>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="L13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>1.276E7</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S12" s="6" t="inlineStr">
+      <c r="S13" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
